--- a/results/federated/final_summary/summary.xlsx
+++ b/results/federated/final_summary/summary.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-04T00:17:29+00:00</t>
+          <t>2026-08-07T13:00:19+00:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -805,10 +805,10 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N3" t="n">
-        <v>313</v>
+        <v>622</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -827,58 +827,58 @@
         <v>0.5112</v>
       </c>
       <c r="S3" t="n">
-        <v>0.403</v>
+        <v>0.4328</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3742</v>
+        <v>0.3949</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3915</v>
+        <v>0.3939</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3742</v>
+        <v>0.3949</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3744</v>
+        <v>0.3931</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5594</v>
+        <v>0.5816</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5569</v>
+        <v>0.5716</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.6484</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.4928</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5179</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.383</v>
+        <v>0.4224</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2222</v>
+        <v>0.2241</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5702</v>
+        <v>0.5656</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4286</v>
+        <v>0.4096</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.1758</v>
+        <v>0.2063</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.4745</v>
+        <v>0.5036</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.3462</v>
+        <v>0.4359</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.3019</v>
+        <v>0.2453</v>
       </c>
     </row>
     <row r="4">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-04T00:41:01+00:00</t>
+          <t>2026-08-07T00:36:01+00:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>317</v>
+        <v>779</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1347,58 +1347,58 @@
         <v>0.5112</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4776</v>
+        <v>0.4925</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4522</v>
+        <v>0.4327</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4646</v>
+        <v>0.4574</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4522</v>
+        <v>0.4327</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4378</v>
+        <v>0.4338</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6531</v>
+        <v>0.6077</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6667</v>
+        <v>0.6222</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6845</v>
+        <v>0.6565</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6082</v>
+        <v>0.5443</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6015</v>
+        <v>0.6294</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3607</v>
+        <v>0.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.3514</v>
+        <v>0.272</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.6202</v>
+        <v>0.604</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.5</v>
+        <v>0.5319</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.2737</v>
+        <v>0.2361</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.5839</v>
+        <v>0.6569</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.2821</v>
+        <v>0.3205</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.4906</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="8">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-04T00:59:41+00:00</t>
+          <t>2026-08-06T12:12:04+00:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1715,10 +1715,10 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="N10" t="n">
-        <v>387</v>
+        <v>849</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1737,58 +1737,58 @@
         <v>0.5112</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4515</v>
+        <v>0.4776</v>
       </c>
       <c r="T10" t="n">
-        <v>0.421</v>
+        <v>0.4285</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4365</v>
+        <v>0.4449</v>
       </c>
       <c r="V10" t="n">
-        <v>0.421</v>
+        <v>0.4285</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4197</v>
+        <v>0.4301</v>
       </c>
       <c r="X10" t="n">
-        <v>0.625</v>
+        <v>0.6152</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.6394</v>
+        <v>0.6091</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.6811</v>
+        <v>0.7043</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.5545</v>
+        <v>0.5322</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.5594</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.4265</v>
+        <v>0.4211</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.2734</v>
+        <v>0.2698</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.5887</v>
+        <v>0.5929</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.5</v>
+        <v>0.5091</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.2209</v>
+        <v>0.2329</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.6058</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.3718</v>
+        <v>0.359</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.3585</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="11">
@@ -3081,26 +3081,26 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.4776</v>
+        <v>0.4925</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4646</v>
+        <v>0.4574</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4522</v>
+        <v>0.4327</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4378</v>
+        <v>0.4338</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6531</v>
+        <v>0.6077</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>317</v>
+        <v>779</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>0.6068</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0463</v>
+        <v>0.0009</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -3451,26 +3451,26 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.4515</v>
+        <v>0.4776</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4365</v>
+        <v>0.4449</v>
       </c>
       <c r="I4" t="n">
-        <v>0.421</v>
+        <v>0.4285</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4197</v>
+        <v>0.4301</v>
       </c>
       <c r="K4" t="n">
-        <v>0.625</v>
+        <v>0.6152</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="N4" t="n">
-        <v>387</v>
+        <v>849</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>0.6068</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0182</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -3498,20 +3498,4586 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:AH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>experiment</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>partition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n_train_patients</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_train_images</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>n_val_patients</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>n_val_images</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>val_patients_HRposHER2neg</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>val_patients_TripleNeg</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>val_patients_HER2pos</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>trivial_baseline</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>balanced_accuracy</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>macro_auc</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>auc_HRposHER2neg</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>auc_TripleNeg</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>auc_HER2pos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>precision_HRposHER2neg</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>precision_TripleNeg</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>precision_HER2pos</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>recall_HRposHER2neg</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>recall_TripleNeg</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>recall_HER2pos</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>f1_HRposHER2neg</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>f1_TripleNeg</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>f1_HER2pos</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>confusion</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>no rows</t>
+          <t>test02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>test02_fedavg_2h</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hospital_1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>612</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4870</v>
+      </c>
+      <c r="J2" t="n">
+        <v>152</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1214</v>
+      </c>
+      <c r="L2" t="n">
+        <v>77</v>
+      </c>
+      <c r="M2" t="n">
+        <v>41</v>
+      </c>
+      <c r="N2" t="n">
+        <v>34</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.5066000000000001</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.5526</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.5294</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.5306</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.5294</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.5259</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.6572</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.6778999999999999</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.6955</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.5982</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.7015</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.5641</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.6104000000000001</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5366</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.6528</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[[47, 8, 22], [10, 22, 9], [10, 9, 15]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>test02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>test02_fedavg_2h</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hospital_2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>611</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4849</v>
+      </c>
+      <c r="J3" t="n">
+        <v>152</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1198</v>
+      </c>
+      <c r="L3" t="n">
+        <v>77</v>
+      </c>
+      <c r="M3" t="n">
+        <v>41</v>
+      </c>
+      <c r="N3" t="n">
+        <v>34</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5066000000000001</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.5785</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.6149</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.5558999999999999</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.5648</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.6032</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.4935</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.5429</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[[38, 22, 17], [15, 16, 10], [10, 12, 12]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>test03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>test03_fedprox_2h</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>hospital_1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>612</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4870</v>
+      </c>
+      <c r="J4" t="n">
+        <v>152</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1214</v>
+      </c>
+      <c r="L4" t="n">
+        <v>77</v>
+      </c>
+      <c r="M4" t="n">
+        <v>41</v>
+      </c>
+      <c r="N4" t="n">
+        <v>34</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5066000000000001</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4868</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.6498</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.6644</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.6719000000000001</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5584</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.4634</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.6099</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.4419</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[[43, 15, 19], [10, 19, 12], [11, 11, 12]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>test03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test03_fedprox_2h</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hospital_2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>611</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4849</v>
+      </c>
+      <c r="J5" t="n">
+        <v>152</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1198</v>
+      </c>
+      <c r="L5" t="n">
+        <v>77</v>
+      </c>
+      <c r="M5" t="n">
+        <v>41</v>
+      </c>
+      <c r="N5" t="n">
+        <v>34</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5066000000000001</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.4117</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.6385999999999999</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5489000000000001</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.5364</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.6143</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.5584</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[[43, 15, 19], [14, 17, 10], [13, 12, 9]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>test04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test04_fedavg_3h</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>hospital_1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>408</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3245</v>
+      </c>
+      <c r="J6" t="n">
+        <v>102</v>
+      </c>
+      <c r="K6" t="n">
+        <v>816</v>
+      </c>
+      <c r="L6" t="n">
+        <v>52</v>
+      </c>
+      <c r="M6" t="n">
+        <v>27</v>
+      </c>
+      <c r="N6" t="n">
+        <v>23</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.6307</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.6204</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.6311</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.6405999999999999</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.5577</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.5686</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[[29, 12, 11], [11, 10, 6], [10, 6, 7]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>test04</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>test04_fedavg_3h</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>hospital_2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>408</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3249</v>
+      </c>
+      <c r="J7" t="n">
+        <v>102</v>
+      </c>
+      <c r="K7" t="n">
+        <v>814</v>
+      </c>
+      <c r="L7" t="n">
+        <v>52</v>
+      </c>
+      <c r="M7" t="n">
+        <v>27</v>
+      </c>
+      <c r="N7" t="n">
+        <v>23</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.6381</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.6158</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.6558</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.6428</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.4815</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.5306</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.4407</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[[26, 13, 13], [10, 13, 4], [10, 6, 7]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>test04</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>test04_fedavg_3h</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>hospital_3</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>406</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3206</v>
+      </c>
+      <c r="J8" t="n">
+        <v>101</v>
+      </c>
+      <c r="K8" t="n">
+        <v>801</v>
+      </c>
+      <c r="L8" t="n">
+        <v>51</v>
+      </c>
+      <c r="M8" t="n">
+        <v>27</v>
+      </c>
+      <c r="N8" t="n">
+        <v>23</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.5347</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4761</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.5986</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.6231</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.5886</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.5842000000000001</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.6863</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.4815</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.6481</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.4643</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[[35, 9, 7], [12, 13, 2], [10, 7, 6]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>test05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>test05_fedprox_3h</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hospital_1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>408</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3245</v>
+      </c>
+      <c r="J9" t="n">
+        <v>102</v>
+      </c>
+      <c r="K9" t="n">
+        <v>816</v>
+      </c>
+      <c r="L9" t="n">
+        <v>52</v>
+      </c>
+      <c r="M9" t="n">
+        <v>27</v>
+      </c>
+      <c r="N9" t="n">
+        <v>23</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4377</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.4275</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.4377</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.6529</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.6362</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.6797</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.5957</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.4783</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.5657</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.4151</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[[28, 12, 12], [12, 8, 7], [7, 5, 11]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>test05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>test05_fedprox_3h</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>hospital_2</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>408</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3249</v>
+      </c>
+      <c r="J10" t="n">
+        <v>102</v>
+      </c>
+      <c r="K10" t="n">
+        <v>814</v>
+      </c>
+      <c r="L10" t="n">
+        <v>52</v>
+      </c>
+      <c r="M10" t="n">
+        <v>27</v>
+      </c>
+      <c r="N10" t="n">
+        <v>23</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.6189</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.6459</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.5707</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.5909</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.5417</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[[26, 9, 17], [7, 12, 8], [11, 4, 8]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>test05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>test05_fedprox_3h</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>hospital_3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>406</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3206</v>
+      </c>
+      <c r="J11" t="n">
+        <v>101</v>
+      </c>
+      <c r="K11" t="n">
+        <v>801</v>
+      </c>
+      <c r="L11" t="n">
+        <v>51</v>
+      </c>
+      <c r="M11" t="n">
+        <v>27</v>
+      </c>
+      <c r="N11" t="n">
+        <v>23</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.5149</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4573</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4616</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.4573</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.4575</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.6307</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.6471</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.6446</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.6002999999999999</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.6071</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.6355</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[[34, 9, 8], [11, 12, 4], [11, 6, 6]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>test06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>test06_fedavg_4h</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>hospital_1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>306</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2439</v>
+      </c>
+      <c r="J12" t="n">
+        <v>77</v>
+      </c>
+      <c r="K12" t="n">
+        <v>614</v>
+      </c>
+      <c r="L12" t="n">
+        <v>39</v>
+      </c>
+      <c r="M12" t="n">
+        <v>21</v>
+      </c>
+      <c r="N12" t="n">
+        <v>17</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.4191</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.4253</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4191</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.6101</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.5972</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.6556</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.5775</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5814</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.6098</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[[25, 5, 9], [10, 8, 3], [8, 5, 4]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>test06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>test06_fedavg_4h</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>hospital_2</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>305</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2423</v>
+      </c>
+      <c r="J13" t="n">
+        <v>77</v>
+      </c>
+      <c r="K13" t="n">
+        <v>616</v>
+      </c>
+      <c r="L13" t="n">
+        <v>39</v>
+      </c>
+      <c r="M13" t="n">
+        <v>21</v>
+      </c>
+      <c r="N13" t="n">
+        <v>17</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.5493</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.5578</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.5608</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.5581</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.2381</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.5854</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[[24, 7, 8], [11, 5, 5], [8, 6, 3]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>test06</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>test06_fedavg_4h</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>hospital_3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>305</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2426</v>
+      </c>
+      <c r="J14" t="n">
+        <v>76</v>
+      </c>
+      <c r="K14" t="n">
+        <v>608</v>
+      </c>
+      <c r="L14" t="n">
+        <v>39</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20</v>
+      </c>
+      <c r="N14" t="n">
+        <v>17</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.5395</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4515</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4711</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.4515</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.4521</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.7026</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.7166</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.6705</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.7208</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.6122</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.7692</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.6818</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[[30, 4, 5], [11, 7, 2], [8, 5, 4]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>test06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>test06_fedavg_4h</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>hospital_4</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>305</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2399</v>
+      </c>
+      <c r="J15" t="n">
+        <v>76</v>
+      </c>
+      <c r="K15" t="n">
+        <v>606</v>
+      </c>
+      <c r="L15" t="n">
+        <v>39</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20</v>
+      </c>
+      <c r="N15" t="n">
+        <v>17</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.4868</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.4255</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.5606</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.6518</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.5852000000000001</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5814</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.6098</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[[25, 7, 7], [10, 8, 2], [8, 5, 4]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>test07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>test07_fedprox_4h</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>hospital_1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>306</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2439</v>
+      </c>
+      <c r="J16" t="n">
+        <v>77</v>
+      </c>
+      <c r="K16" t="n">
+        <v>614</v>
+      </c>
+      <c r="L16" t="n">
+        <v>39</v>
+      </c>
+      <c r="M16" t="n">
+        <v>21</v>
+      </c>
+      <c r="N16" t="n">
+        <v>17</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.4398</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.6433</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.6242</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.7185</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.5873</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.6389</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.5897</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.6133</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[[23, 5, 11], [9, 8, 4], [4, 7, 6]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>test07</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>test07_fedprox_4h</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>hospital_2</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>305</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2423</v>
+      </c>
+      <c r="J17" t="n">
+        <v>77</v>
+      </c>
+      <c r="K17" t="n">
+        <v>616</v>
+      </c>
+      <c r="L17" t="n">
+        <v>39</v>
+      </c>
+      <c r="M17" t="n">
+        <v>21</v>
+      </c>
+      <c r="N17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.4416</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.6181</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.5587</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.5745</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.5946</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.5641</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.5789</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[[22, 11, 6], [8, 7, 6], [7, 5, 5]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>test07</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>test07_fedprox_4h</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>hospital_3</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>305</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2426</v>
+      </c>
+      <c r="J18" t="n">
+        <v>76</v>
+      </c>
+      <c r="K18" t="n">
+        <v>608</v>
+      </c>
+      <c r="L18" t="n">
+        <v>39</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20</v>
+      </c>
+      <c r="N18" t="n">
+        <v>17</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.4737</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.6338</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.6625</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.6348</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.6042</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.6279</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.6923</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[[27, 5, 7], [8, 8, 4], [8, 8, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>test07</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>test07_fedprox_4h</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4_clients_balanced</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>hospital_4</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>305</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2399</v>
+      </c>
+      <c r="J19" t="n">
+        <v>76</v>
+      </c>
+      <c r="K19" t="n">
+        <v>606</v>
+      </c>
+      <c r="L19" t="n">
+        <v>39</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20</v>
+      </c>
+      <c r="N19" t="n">
+        <v>17</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.5785</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.5184</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.6437</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.5733</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.5278</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.4872</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.5067</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.3684</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[[19, 7, 13], [10, 7, 3], [7, 4, 6]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>test08</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>test08_fedavg_skewed</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4_clients_skewed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>hospital_1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>678</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5395</v>
+      </c>
+      <c r="J20" t="n">
+        <v>170</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1358</v>
+      </c>
+      <c r="L20" t="n">
+        <v>86</v>
+      </c>
+      <c r="M20" t="n">
+        <v>46</v>
+      </c>
+      <c r="N20" t="n">
+        <v>38</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.5059</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.5118</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.4674</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.4682</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.6383</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.6602</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.6021</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.6341</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.6047</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[[52, 20, 14], [13, 24, 9], [17, 10, 11]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>test08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>test08_fedavg_skewed</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4_clients_skewed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>hospital_2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>273</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2171</v>
+      </c>
+      <c r="J21" t="n">
+        <v>67</v>
+      </c>
+      <c r="K21" t="n">
+        <v>534</v>
+      </c>
+      <c r="L21" t="n">
+        <v>34</v>
+      </c>
+      <c r="M21" t="n">
+        <v>18</v>
+      </c>
+      <c r="N21" t="n">
+        <v>15</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.5373</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.5196</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.5066000000000001</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.5196</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.5062</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.7527</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.7077</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.7619</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.7885</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.6552</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.5588</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.6032</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.5581</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[[19, 10, 5], [3, 12, 3], [7, 3, 5]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>test08</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>test08_fedavg_skewed</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4_clients_skewed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>hospital_3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>136</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1073</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34</v>
+      </c>
+      <c r="K22" t="n">
+        <v>266</v>
+      </c>
+      <c r="L22" t="n">
+        <v>17</v>
+      </c>
+      <c r="M22" t="n">
+        <v>9</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.5225</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.4267</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.5769</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.6923</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.5294</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[[9, 6, 2], [3, 3, 3], [1, 4, 3]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>test08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>test08_fedavg_skewed</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4_clients_skewed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>hospital_4</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>135</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1066</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34</v>
+      </c>
+      <c r="K23" t="n">
+        <v>268</v>
+      </c>
+      <c r="L23" t="n">
+        <v>17</v>
+      </c>
+      <c r="M23" t="n">
+        <v>9</v>
+      </c>
+      <c r="N23" t="n">
+        <v>8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.5583</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.5443</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.5583</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.5502</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.6698</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.6713</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.8044</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.6471</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.6471</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.6471</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.7368</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[[11, 1, 5], [2, 7, 0], [4, 2, 2]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>test09</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>test09_fedprox_skewed</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4_clients_skewed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>hospital_1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>678</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5395</v>
+      </c>
+      <c r="J24" t="n">
+        <v>170</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1358</v>
+      </c>
+      <c r="L24" t="n">
+        <v>86</v>
+      </c>
+      <c r="M24" t="n">
+        <v>46</v>
+      </c>
+      <c r="N24" t="n">
+        <v>38</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.5059</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.5118</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.4561</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.4564</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.6333</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.6662</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.5815</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.6437</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.4468</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.6512</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.6474</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.2703</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[[56, 15, 15], [14, 21, 11], [17, 11, 10]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>test09</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>test09_fedprox_skewed</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4_clients_skewed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>hospital_2</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>273</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2171</v>
+      </c>
+      <c r="J25" t="n">
+        <v>67</v>
+      </c>
+      <c r="K25" t="n">
+        <v>534</v>
+      </c>
+      <c r="L25" t="n">
+        <v>34</v>
+      </c>
+      <c r="M25" t="n">
+        <v>18</v>
+      </c>
+      <c r="N25" t="n">
+        <v>15</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.5588</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.5496</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.5588</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.5514</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.7496</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.7789</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.7321</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.5455</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.6765</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[[23, 6, 5], [3, 12, 3], [6, 4, 5]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>test09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>test09_fedprox_skewed</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4_clients_skewed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>hospital_3</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>136</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1073</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34</v>
+      </c>
+      <c r="K26" t="n">
+        <v>266</v>
+      </c>
+      <c r="L26" t="n">
+        <v>17</v>
+      </c>
+      <c r="M26" t="n">
+        <v>9</v>
+      </c>
+      <c r="N26" t="n">
+        <v>8</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.4706</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.5643</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.5813</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.5155999999999999</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.5962</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.6061</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[[10, 5, 2], [3, 4, 2], [3, 3, 2]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>test09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>test09_fedprox_skewed</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4_clients_skewed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>hospital_4</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>135</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1066</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34</v>
+      </c>
+      <c r="K27" t="n">
+        <v>268</v>
+      </c>
+      <c r="L27" t="n">
+        <v>17</v>
+      </c>
+      <c r="M27" t="n">
+        <v>9</v>
+      </c>
+      <c r="N27" t="n">
+        <v>8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.4542</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.6252</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.8133</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.4567</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.6061</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[[10, 1, 6], [2, 6, 1], [4, 3, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>test10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>test10_fedavg_cohort</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3_clients_cohort</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>hospital_1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>514</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4067</v>
+      </c>
+      <c r="J28" t="n">
+        <v>128</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1007</v>
+      </c>
+      <c r="L28" t="n">
+        <v>85</v>
+      </c>
+      <c r="M28" t="n">
+        <v>20</v>
+      </c>
+      <c r="N28" t="n">
+        <v>23</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.6168</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.5593</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.6791</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.4941</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.5957</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[[42, 35, 8], [7, 10, 3], [7, 10, 6]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>test10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>test10_fedavg_cohort</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3_clients_cohort</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>hospital_2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>82</v>
+      </c>
+      <c r="I29" t="n">
+        <v>652</v>
+      </c>
+      <c r="J29" t="n">
+        <v>19</v>
+      </c>
+      <c r="K29" t="n">
+        <v>152</v>
+      </c>
+      <c r="L29" t="n">
+        <v>8</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>6</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.3684</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.2205</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.2571</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.4837</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[[6, 2, 0], [3, 1, 1], [4, 2, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>test10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>test10_fedavg_cohort</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3_clients_cohort</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>hospital_3</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>627</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5005</v>
+      </c>
+      <c r="J30" t="n">
+        <v>157</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1248</v>
+      </c>
+      <c r="L30" t="n">
+        <v>61</v>
+      </c>
+      <c r="M30" t="n">
+        <v>56</v>
+      </c>
+      <c r="N30" t="n">
+        <v>40</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.4522</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.4255</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.4255</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.5802</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.5458</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.6054</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.5895</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.4419</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[[38, 14, 9], [27, 24, 5], [21, 10, 9]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>test12</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>test12_fedavg_sizematched</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3_clients_sizematched</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>hospital_1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>514</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4096</v>
+      </c>
+      <c r="J31" t="n">
+        <v>128</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1020</v>
+      </c>
+      <c r="L31" t="n">
+        <v>65</v>
+      </c>
+      <c r="M31" t="n">
+        <v>34</v>
+      </c>
+      <c r="N31" t="n">
+        <v>29</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.5078</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.6343</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.6911</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.6367</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.5750999999999999</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.6296</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.2571</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.5231</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[[34, 16, 15], [11, 12, 11], [9, 11, 9]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>test12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>test12_fedavg_sizematched</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3_clients_sizematched</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>hospital_2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>81</v>
+      </c>
+      <c r="I32" t="n">
+        <v>640</v>
+      </c>
+      <c r="J32" t="n">
+        <v>20</v>
+      </c>
+      <c r="K32" t="n">
+        <v>160</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.6444</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.7422</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.7467</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.7272999999999999</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[[6, 2, 2], [1, 4, 0], [2, 0, 3]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>test12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>test12_fedavg_sizematched</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>fedavg</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3_clients_sizematched</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>hospital_3</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>628</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4976</v>
+      </c>
+      <c r="J33" t="n">
+        <v>156</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1239</v>
+      </c>
+      <c r="L33" t="n">
+        <v>79</v>
+      </c>
+      <c r="M33" t="n">
+        <v>42</v>
+      </c>
+      <c r="N33" t="n">
+        <v>35</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.4359</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.4032</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.5908</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.5981</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.6122</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.5622</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.5942</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.5541</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[[41, 21, 17], [14, 16, 12], [14, 10, 11]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>test11</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>test11_fedprox_cohort</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3_clients_cohort</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>hospital_1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>514</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4067</v>
+      </c>
+      <c r="J34" t="n">
+        <v>128</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1007</v>
+      </c>
+      <c r="L34" t="n">
+        <v>85</v>
+      </c>
+      <c r="M34" t="n">
+        <v>20</v>
+      </c>
+      <c r="N34" t="n">
+        <v>23</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.6051</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.5574</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.6439</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.7193000000000001</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.5775</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.1961</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[[41, 21, 23], [8, 5, 7], [8, 5, 10]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>test11</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>test11_fedprox_cohort</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3_clients_cohort</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>hospital_2</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>82</v>
+      </c>
+      <c r="I35" t="n">
+        <v>652</v>
+      </c>
+      <c r="J35" t="n">
+        <v>19</v>
+      </c>
+      <c r="K35" t="n">
+        <v>152</v>
+      </c>
+      <c r="L35" t="n">
+        <v>8</v>
+      </c>
+      <c r="M35" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.5263</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.4972</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.4868</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.4972</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.6274</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.7386</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.7436</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[[5, 2, 1], [2, 1, 2], [2, 0, 4]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>test11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>test11_fedprox_cohort</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3_clients_cohort</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>hospital_3</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>627</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5005</v>
+      </c>
+      <c r="J36" t="n">
+        <v>157</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1248</v>
+      </c>
+      <c r="L36" t="n">
+        <v>61</v>
+      </c>
+      <c r="M36" t="n">
+        <v>56</v>
+      </c>
+      <c r="N36" t="n">
+        <v>40</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.4076</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.5841</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.5823</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[[39, 12, 10], [31, 16, 9], [21, 10, 9]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>test13</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>test13_fedprox_sizematched</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3_clients_sizematched</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>hospital_1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>514</v>
+      </c>
+      <c r="I37" t="n">
+        <v>4096</v>
+      </c>
+      <c r="J37" t="n">
+        <v>128</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1020</v>
+      </c>
+      <c r="L37" t="n">
+        <v>65</v>
+      </c>
+      <c r="M37" t="n">
+        <v>34</v>
+      </c>
+      <c r="N37" t="n">
+        <v>29</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.5078</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.4922</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.6143</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.5608</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.6308</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.6308</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.6308</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[[41, 13, 11], [13, 13, 8], [11, 9, 9]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>test13</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>test13_fedprox_sizematched</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3_clients_sizematched</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>hospital_2</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>81</v>
+      </c>
+      <c r="I38" t="n">
+        <v>640</v>
+      </c>
+      <c r="J38" t="n">
+        <v>20</v>
+      </c>
+      <c r="K38" t="n">
+        <v>160</v>
+      </c>
+      <c r="L38" t="n">
+        <v>10</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.7333</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.7389</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.7333</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.7313</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.7067</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.7272999999999999</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[[8, 1, 1], [1, 4, 0], [1, 1, 3]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>test13</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>test13_fedprox_sizematched</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>fedprox</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3_clients_sizematched</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>hospital_3</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>628</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4976</v>
+      </c>
+      <c r="J39" t="n">
+        <v>156</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1239</v>
+      </c>
+      <c r="L39" t="n">
+        <v>79</v>
+      </c>
+      <c r="M39" t="n">
+        <v>42</v>
+      </c>
+      <c r="N39" t="n">
+        <v>35</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.5995</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.6332</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.5702</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.5568</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.1852</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.6203</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.5868</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[[49, 18, 12], [21, 11, 10], [18, 12, 5]]</t>
         </is>
       </c>
     </row>
@@ -3608,7 +8174,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-03T23:03:03+00:00</t>
+          <t>2026-08-05T14:00:05+00:00</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -3647,7 +8213,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-03T23:03:11+00:00</t>
+          <t>2026-08-05T14:00:11+00:00</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -3686,7 +8252,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-03T23:03:22+00:00</t>
+          <t>2026-08-05T14:00:17+00:00</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -3725,7 +8291,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-03T23:03:33+00:00</t>
+          <t>2026-08-05T14:00:23+00:00</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -3764,7 +8330,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-05T00:52:03+00:00</t>
+          <t>2026-08-05T14:00:35+00:00</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -3803,7 +8369,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-05T00:52:19+00:00</t>
+          <t>2026-08-05T14:00:29+00:00</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -5965,26 +10531,26 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.403</v>
+        <v>0.4328</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3915</v>
+        <v>0.3939</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3742</v>
+        <v>0.3949</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3744</v>
+        <v>0.3931</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5594</v>
+        <v>0.5816</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N3" t="n">
-        <v>313</v>
+        <v>622</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -5995,7 +10561,7 @@
         <v>0.6068</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0474</v>
+        <v>-0.0252</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -6097,26 +10663,26 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.4776</v>
+        <v>0.4925</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4646</v>
+        <v>0.4574</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4522</v>
+        <v>0.4327</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4378</v>
+        <v>0.4338</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6531</v>
+        <v>0.6077</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>317</v>
+        <v>779</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -6127,7 +10693,7 @@
         <v>0.6068</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0463</v>
+        <v>0.0009</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -6731,26 +11297,26 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.4515</v>
+        <v>0.4776</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4365</v>
+        <v>0.4449</v>
       </c>
       <c r="I6" t="n">
-        <v>0.421</v>
+        <v>0.4285</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4197</v>
+        <v>0.4301</v>
       </c>
       <c r="K6" t="n">
-        <v>0.625</v>
+        <v>0.6152</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="N6" t="n">
-        <v>387</v>
+        <v>849</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -6761,7 +11327,7 @@
         <v>0.6068</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0182</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -7035,26 +11601,26 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.403</v>
+        <v>0.4328</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3915</v>
+        <v>0.3939</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3742</v>
+        <v>0.3949</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3744</v>
+        <v>0.3931</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5594</v>
+        <v>0.5816</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N2" t="n">
-        <v>313</v>
+        <v>622</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -7062,10 +11628,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.5893</v>
+        <v>0.5854</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.0299</v>
+        <v>-0.0039</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -7128,10 +11694,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.5893</v>
+        <v>0.5854</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0097</v>
+        <v>0.0135</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -7167,26 +11733,26 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.4776</v>
+        <v>0.4925</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4646</v>
+        <v>0.4574</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4522</v>
+        <v>0.4327</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4378</v>
+        <v>0.4338</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6531</v>
+        <v>0.6077</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>317</v>
+        <v>779</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -7194,10 +11760,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.5893</v>
+        <v>0.5854</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0638</v>
+        <v>0.0222</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -7260,10 +11826,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.5893</v>
+        <v>0.5854</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0089</v>
+        <v>0.0127</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -7326,10 +11892,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.5893</v>
+        <v>0.5854</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0467</v>
+        <v>-0.0429</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -7392,10 +11958,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.5893</v>
+        <v>0.5854</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0057</v>
+        <v>-0.0019</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -7458,10 +12024,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.5893</v>
+        <v>0.5854</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0024</v>
+        <v>0.0062</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -7524,10 +12090,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.5893</v>
+        <v>0.5854</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0065</v>
+        <v>0.0103</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -7590,10 +12156,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.5893</v>
+        <v>0.5854</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0182</v>
+        <v>0.0221</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -7629,26 +12195,26 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.4515</v>
+        <v>0.4776</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4365</v>
+        <v>0.4449</v>
       </c>
       <c r="I11" t="n">
-        <v>0.421</v>
+        <v>0.4285</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4197</v>
+        <v>0.4301</v>
       </c>
       <c r="K11" t="n">
-        <v>0.625</v>
+        <v>0.6152</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="N11" t="n">
-        <v>387</v>
+        <v>849</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -7656,10 +12222,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.5893</v>
+        <v>0.5854</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0357</v>
+        <v>0.0297</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>
@@ -7722,10 +12288,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.5893</v>
+        <v>0.5854</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.0215</v>
+        <v>-0.0177</v>
       </c>
       <c r="R12" t="b">
         <v>1</v>
@@ -7788,10 +12354,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.5893</v>
+        <v>0.5854</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.0011</v>
+        <v>0.0027</v>
       </c>
       <c r="R13" t="b">
         <v>1</v>
@@ -7948,52 +12514,52 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.403</v>
+        <v>0.4328</v>
       </c>
       <c r="F2" t="n">
         <v>0.4328</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0298</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3915</v>
+        <v>0.3939</v>
       </c>
       <c r="I2" t="n">
         <v>0.4028</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3742</v>
+        <v>0.3949</v>
       </c>
       <c r="K2" t="n">
         <v>0.4025</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3744</v>
+        <v>0.3931</v>
       </c>
       <c r="M2" t="n">
         <v>0.4001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0257</v>
+        <v>0.007</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5594</v>
+        <v>0.5816</v>
       </c>
       <c r="P2" t="n">
         <v>0.5917</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0323</v>
+        <v>0.0101</v>
       </c>
       <c r="R2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S2" t="n">
         <v>29</v>
       </c>
       <c r="T2" t="n">
-        <v>313</v>
+        <v>622</v>
       </c>
       <c r="U2" t="n">
         <v>351</v>
@@ -8264,43 +12830,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4776</v>
+        <v>0.4925</v>
       </c>
       <c r="F6" t="n">
         <v>0.4739</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0037</v>
+        <v>-0.0186</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4646</v>
+        <v>0.4574</v>
       </c>
       <c r="I6" t="n">
         <v>0.4389</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4522</v>
+        <v>0.4327</v>
       </c>
       <c r="K6" t="n">
         <v>0.4393</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4378</v>
+        <v>0.4338</v>
       </c>
       <c r="M6" t="n">
         <v>0.4362</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6531</v>
+        <v>0.6077</v>
       </c>
       <c r="P6" t="n">
         <v>0.6075</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0456</v>
+        <v>-0.0002</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -8309,7 +12875,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>317</v>
+        <v>779</v>
       </c>
       <c r="U6" t="n">
         <v>335</v>
@@ -8346,52 +12912,52 @@
         <v>0.4888</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4515</v>
+        <v>0.4776</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0373</v>
+        <v>-0.0112</v>
       </c>
       <c r="H7" t="n">
         <v>0.4374</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4365</v>
+        <v>0.4449</v>
       </c>
       <c r="J7" t="n">
         <v>0.4259</v>
       </c>
       <c r="K7" t="n">
-        <v>0.421</v>
+        <v>0.4285</v>
       </c>
       <c r="L7" t="n">
         <v>0.4292</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4197</v>
+        <v>0.4301</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0095</v>
+        <v>0.0009</v>
       </c>
       <c r="O7" t="n">
         <v>0.5982</v>
       </c>
       <c r="P7" t="n">
-        <v>0.625</v>
+        <v>0.6152</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0268</v>
+        <v>0.017</v>
       </c>
       <c r="R7" t="n">
         <v>21</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="T7" t="n">
         <v>323</v>
       </c>
       <c r="U7" t="n">
-        <v>387</v>
+        <v>849</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
@@ -8604,26 +13170,26 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.403</v>
+        <v>0.4328</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3915</v>
+        <v>0.3939</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3742</v>
+        <v>0.3949</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3744</v>
+        <v>0.3931</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5594</v>
+        <v>0.5816</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N3" t="n">
-        <v>313</v>
+        <v>622</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -8634,7 +13200,7 @@
         <v>0.6068</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0474</v>
+        <v>-0.0252</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
